--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.88642630903672</v>
+        <v>3.231544275218467</v>
       </c>
       <c r="D2" t="n">
-        <v>19.74998901771457</v>
+        <v>3.209373215378617</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F2" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.314428065937481</v>
+        <v>1.513594560714841</v>
       </c>
       <c r="D3" t="n">
-        <v>9.477512135671617</v>
+        <v>1.540095722046638</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F3" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.57807666398525</v>
+        <v>2.856437457897603</v>
       </c>
       <c r="D4" t="n">
-        <v>17.68803078966084</v>
+        <v>2.874305003319886</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F4" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.12182921941087</v>
+        <v>2.944797248154266</v>
       </c>
       <c r="D5" t="n">
-        <v>18.29346667235737</v>
+        <v>2.972688334258073</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F5" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72939428688193</v>
+        <v>6.781026571618313</v>
       </c>
       <c r="D6" t="n">
-        <v>41.73099801021505</v>
+        <v>6.781287176659945</v>
       </c>
       <c r="E6" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F6" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.54881551907839</v>
+        <v>5.614182521850238</v>
       </c>
       <c r="D7" t="n">
-        <v>34.70467523983828</v>
+        <v>5.639509726473721</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F7" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.4972521430809</v>
+        <v>7.718303473250646</v>
       </c>
       <c r="D8" t="n">
-        <v>47.37092307399283</v>
+        <v>7.697774999523836</v>
       </c>
       <c r="E8" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F8" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.48455382180451</v>
+        <v>5.116239996043234</v>
       </c>
       <c r="D9" t="n">
-        <v>31.37252908818237</v>
+        <v>5.098035976829635</v>
       </c>
       <c r="E9" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F9" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.52384268776739</v>
+        <v>5.772624436762201</v>
       </c>
       <c r="D10" t="n">
-        <v>35.39748228845314</v>
+        <v>5.752090871873635</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F10" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.57751322323812</v>
+        <v>1.718845898776194</v>
       </c>
       <c r="D11" t="n">
-        <v>10.67969139152586</v>
+        <v>1.735449851122951</v>
       </c>
       <c r="E11" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F11" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83469525183551</v>
+        <v>2.57313797842327</v>
       </c>
       <c r="D12" t="n">
-        <v>16.04858154244524</v>
+        <v>2.607894500647352</v>
       </c>
       <c r="E12" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F12" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.867110473544964</v>
+        <v>1.278405451951057</v>
       </c>
       <c r="D13" t="n">
-        <v>7.883083784230556</v>
+        <v>1.281001114937465</v>
       </c>
       <c r="E13" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F13" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.10709862815198</v>
+        <v>3.267403527074698</v>
       </c>
       <c r="D14" t="n">
-        <v>20.13704261491707</v>
+        <v>3.272269424924025</v>
       </c>
       <c r="E14" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F14" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.65481347116045</v>
+        <v>5.631407189063574</v>
       </c>
       <c r="D15" t="n">
-        <v>34.57493673680382</v>
+        <v>5.618427219730621</v>
       </c>
       <c r="E15" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F15" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.67298624299698</v>
+        <v>3.521860264487009</v>
       </c>
       <c r="D16" t="n">
-        <v>21.78292917446169</v>
+        <v>3.539725990850024</v>
       </c>
       <c r="E16" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F16" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>23.12593156688503</v>
+        <v>3.757963879618818</v>
       </c>
       <c r="D17" t="n">
-        <v>23.33645937044683</v>
+        <v>3.79217464769761</v>
       </c>
       <c r="E17" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F17" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.45169029767695</v>
+        <v>5.273399673372506</v>
       </c>
       <c r="D18" t="n">
-        <v>32.57545812007287</v>
+        <v>5.293511944511843</v>
       </c>
       <c r="E18" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F18" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>23.8183633175526</v>
+        <v>3.870484039102298</v>
       </c>
       <c r="D19" t="n">
-        <v>23.73368577700633</v>
+        <v>3.856723938763528</v>
       </c>
       <c r="E19" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F19" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>15.56835032657766</v>
+        <v>2.52985692806887</v>
       </c>
       <c r="D20" t="n">
-        <v>15.39466953125009</v>
+        <v>2.50163379882814</v>
       </c>
       <c r="E20" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F20" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>41.75816349816422</v>
+        <v>6.785701568451686</v>
       </c>
       <c r="D21" t="n">
-        <v>41.65105468398197</v>
+        <v>6.76829638614707</v>
       </c>
       <c r="E21" t="n">
-        <v>11.28732104201487</v>
+        <v>1.834189669327416</v>
       </c>
       <c r="F21" t="n">
-        <v>11.23551620303015</v>
+        <v>1.8257713829924</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
